--- a/Life Style Diseases Medication.xlsx
+++ b/Life Style Diseases Medication.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Githinji\Desktop\Hospital Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7BE45FA-6401-49BE-A143-8472D197304D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B58620B-84DF-464D-A80F-7AEDB2A42CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{800F38F8-BFEB-446A-BF66-0A72161C9401}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{800F38F8-BFEB-446A-BF66-0A72161C9401}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Cancer Common LSD" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
+    <sheet name="Chemotherapy Com Medication" sheetId="2" r:id="rId3"/>
+    <sheet name="Targeted Therapy Com Medication" sheetId="3" r:id="rId4"/>
+    <sheet name="Immunotherapy Com Medications" sheetId="4" r:id="rId5"/>
+    <sheet name="Hormone Therapy Com Medication" sheetId="5" r:id="rId6"/>
+    <sheet name="Tropical-Treatments Com Medctns" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,10 +39,191 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
+  <si>
+    <t>Chemotherapy</t>
+  </si>
+  <si>
+    <t>Targeted Therapy</t>
+  </si>
+  <si>
+    <t>Immunotherapy</t>
+  </si>
+  <si>
+    <t>Breast Cancer</t>
+  </si>
+  <si>
+    <t>Lung Cancer</t>
+  </si>
+  <si>
+    <t>Prostate Cancer</t>
+  </si>
+  <si>
+    <t>Colorectal Cancer</t>
+  </si>
+  <si>
+    <t>Skin Cancer</t>
+  </si>
+  <si>
+    <t>Cyclophosphamide</t>
+  </si>
+  <si>
+    <t>Doxorubicin</t>
+  </si>
+  <si>
+    <t>Paclitaxel</t>
+  </si>
+  <si>
+    <t>Docetaxel</t>
+  </si>
+  <si>
+    <t>Trastuzumab</t>
+  </si>
+  <si>
+    <t>Pertuzumab</t>
+  </si>
+  <si>
+    <t>Anastrozole,</t>
+  </si>
+  <si>
+    <t>Letrozole</t>
+  </si>
+  <si>
+    <t>Exemestane</t>
+  </si>
+  <si>
+    <t> Tamoxifen </t>
+  </si>
+  <si>
+    <t> Pembrolizumab</t>
+  </si>
+  <si>
+    <t>Cisplatin</t>
+  </si>
+  <si>
+    <t>Carboplatin</t>
+  </si>
+  <si>
+    <t>Gemcitabine</t>
+  </si>
+  <si>
+    <t>Pemetrexed. </t>
+  </si>
+  <si>
+    <t>pembrolizumab</t>
+  </si>
+  <si>
+    <t> nivolumab </t>
+  </si>
+  <si>
+    <t>Cemiplimab</t>
+  </si>
+  <si>
+    <t>Vismodegib</t>
+  </si>
+  <si>
+    <t>Hormone Therapy</t>
+  </si>
+  <si>
+    <t>Tropical Treatments</t>
+  </si>
+  <si>
+    <t> Fluorouracil</t>
+  </si>
+  <si>
+    <t>Imiquimod</t>
+  </si>
+  <si>
+    <t>Leuprolide</t>
+  </si>
+  <si>
+    <t>Bicalutamide</t>
+  </si>
+  <si>
+    <t>Goserelin</t>
+  </si>
+  <si>
+    <t>Enzalutamide</t>
+  </si>
+  <si>
+    <t>Bevacizumab</t>
+  </si>
+  <si>
+    <t>Cetuximab</t>
+  </si>
+  <si>
+    <t>Panitumumab</t>
+  </si>
+  <si>
+    <t>Abiraterone</t>
+  </si>
+  <si>
+    <t>Apalutamide</t>
+  </si>
+  <si>
+    <t> Gefitinib</t>
+  </si>
+  <si>
+    <t>Erlotinib</t>
+  </si>
+  <si>
+    <t>Osimertinib</t>
+  </si>
+  <si>
+    <t>Crizotinib</t>
+  </si>
+  <si>
+    <t> Docetaxel</t>
+  </si>
+  <si>
+    <t>Cabazitaxel </t>
+  </si>
+  <si>
+    <t>5-fluorouracil (5-FU)</t>
+  </si>
+  <si>
+    <t>Irinotecan</t>
+  </si>
+  <si>
+    <t>Oxaliplatin</t>
+  </si>
+  <si>
+    <t> Capecitabine</t>
+  </si>
+  <si>
+    <t>Cancer Type</t>
+  </si>
+  <si>
+    <t>Medication Name</t>
+  </si>
+  <si>
+    <t>Mode of Medication</t>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+  </si>
+  <si>
+    <t>Pembrolizumab</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -64,8 +251,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,9 +573,467 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAA5D79-6521-4D97-83AC-2F9FFE4F316A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EE1BFC-8F6D-48B7-82E9-622F36DFF5A7}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546353EF-2ADB-4FAB-AD1F-C501D25736E9}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1D83F9-5ECF-4C40-B9AD-23FBA456864A}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201A86A0-E262-4AC9-B3AC-D22BC43DA286}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE798776-E58D-49EB-AA38-984838DCEE5E}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBD6F4A-1B15-4FC0-86CB-277D91F094AD}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Life Style Diseases Medication.xlsx
+++ b/Life Style Diseases Medication.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Githinji\Desktop\Hospital Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B58620B-84DF-464D-A80F-7AEDB2A42CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529371CD-3BEA-4D7F-AAD0-8B9F8D1D398E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{800F38F8-BFEB-446A-BF66-0A72161C9401}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="2" xr2:uid="{800F38F8-BFEB-446A-BF66-0A72161C9401}"/>
   </bookViews>
   <sheets>
     <sheet name="Cancer Common LSD" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
-    <sheet name="Chemotherapy Com Medication" sheetId="2" r:id="rId3"/>
+    <sheet name="Chemotherapy Com Medication" sheetId="2" r:id="rId2"/>
+    <sheet name="Cleaned Data" sheetId="8" r:id="rId3"/>
     <sheet name="Targeted Therapy Com Medication" sheetId="3" r:id="rId4"/>
     <sheet name="Immunotherapy Com Medications" sheetId="4" r:id="rId5"/>
     <sheet name="Hormone Therapy Com Medication" sheetId="5" r:id="rId6"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="95">
   <si>
     <t>Chemotherapy</t>
   </si>
@@ -201,20 +201,142 @@
     <t>Mode of Medication</t>
   </si>
   <si>
-    <t>Tamoxifen</t>
-  </si>
-  <si>
     <t>Pembrolizumab</t>
   </si>
   <si>
-    <t>...</t>
+    <t>Anastrozole</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Colorectal Cancer</t>
+  </si>
+  <si>
+    <t>Gefitinib</t>
+  </si>
+  <si>
+    <t>Tamoxifen </t>
+  </si>
+  <si>
+    <t>Nivolumab </t>
+  </si>
+  <si>
+    <t>Fluorouracil</t>
+  </si>
+  <si>
+    <t>Capecitabine</t>
+  </si>
+  <si>
+    <t>Medication Cost</t>
+  </si>
+  <si>
+    <t>Srength</t>
+  </si>
+  <si>
+    <t>Price Ration</t>
+  </si>
+  <si>
+    <t>Price Variation(%)</t>
+  </si>
+  <si>
+    <t>50 mg</t>
+  </si>
+  <si>
+    <t>10 mg - 20 mg</t>
+  </si>
+  <si>
+    <t>100mg</t>
+  </si>
+  <si>
+    <t>80 mg</t>
+  </si>
+  <si>
+    <t>440 mg</t>
+  </si>
+  <si>
+    <t>420 mg</t>
+  </si>
+  <si>
+    <t>2.5 mg</t>
+  </si>
+  <si>
+    <t>1mg</t>
+  </si>
+  <si>
+    <t>25 mg</t>
+  </si>
+  <si>
+    <t>20 mg</t>
+  </si>
+  <si>
+    <t>100 mg</t>
+  </si>
+  <si>
+    <t>Maximum Price(KES)</t>
+  </si>
+  <si>
+    <t>Minimum Price(KES)</t>
+  </si>
+  <si>
+    <t>450 mg</t>
+  </si>
+  <si>
+    <t>200 mg -1g</t>
+  </si>
+  <si>
+    <t>100 mg - 500 mg</t>
+  </si>
+  <si>
+    <t>250 mg</t>
+  </si>
+  <si>
+    <t>150 mg</t>
+  </si>
+  <si>
+    <t>40 mg</t>
+  </si>
+  <si>
+    <t>40 mg - 100 mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 mg </t>
+  </si>
+  <si>
+    <t>40 g</t>
+  </si>
+  <si>
+    <t>350 mg</t>
+  </si>
+  <si>
+    <t>5 mg/mL × 20 mL</t>
+  </si>
+  <si>
+    <t>100 mg - 400 mg</t>
+  </si>
+  <si>
+    <t>500 mg</t>
+  </si>
+  <si>
+    <t>500 mg - 1,000 mg</t>
+  </si>
+  <si>
+    <t>10.8 mg / 11.25 mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75 mg - 11.25 mg </t>
+  </si>
+  <si>
+    <t>60 mg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_([$KES]\ * #,##0_);_([$KES]\ * \(#,##0\);_([$KES]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_([$KES]\ * #,##0.00_);_([$KES]\ * \(#,##0.00\);_([$KES]\ * &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +346,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -248,10 +377,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -259,8 +389,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -667,76 +809,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EE1BFC-8F6D-48B7-82E9-622F36DFF5A7}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="33.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546353EF-2ADB-4FAB-AD1F-C501D25736E9}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -822,6 +894,898 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDBE12B-7ABC-4247-B6FB-8D0024E7390E}">
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="21" style="5" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="5">
+        <v>6200</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="6">
+        <v>26600</v>
+      </c>
+      <c r="G3" s="8">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="5">
+        <v>5320</v>
+      </c>
+      <c r="G4" s="8">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5">
+        <v>25985</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="5">
+        <v>157500</v>
+      </c>
+      <c r="G6" s="8">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="5">
+        <v>399000</v>
+      </c>
+      <c r="G7" s="8">
+        <v>399000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="5">
+        <v>7630</v>
+      </c>
+      <c r="G8" s="8">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5819</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7800</v>
+      </c>
+      <c r="G10" s="8">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3982</v>
+      </c>
+      <c r="G11" s="8">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="5">
+        <v>492100</v>
+      </c>
+      <c r="G12" s="8">
+        <v>230664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7560</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="5">
+        <v>8050</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4655</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="5">
+        <v>7650</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="5">
+        <v>23500</v>
+      </c>
+      <c r="G17" s="8">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="5">
+        <v>10626</v>
+      </c>
+      <c r="G18" s="8">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="5">
+        <v>21880</v>
+      </c>
+      <c r="G19" s="8">
+        <v>15760.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="5">
+        <v>74000</v>
+      </c>
+      <c r="G20" s="8">
+        <v>42826</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="5">
+        <v>273000</v>
+      </c>
+      <c r="G21" s="8">
+        <v>169000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="5">
+        <v>492100</v>
+      </c>
+      <c r="G22" s="8">
+        <v>224664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="5">
+        <v>159600</v>
+      </c>
+      <c r="G23" s="8">
+        <v>42398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="5">
+        <v>8050</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="5">
+        <v>50540</v>
+      </c>
+      <c r="G25" s="8">
+        <v>32300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="5">
+        <v>157555</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="5">
+        <v>240600</v>
+      </c>
+      <c r="G27" s="8">
+        <v>122360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="5">
+        <v>31976</v>
+      </c>
+      <c r="G28" s="8">
+        <v>6480</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="5">
+        <v>43070</v>
+      </c>
+      <c r="G29" s="8">
+        <v>39383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="5">
+        <v>17100</v>
+      </c>
+      <c r="G30" s="8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1020</v>
+      </c>
+      <c r="G31" s="8">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1417</v>
+      </c>
+      <c r="G32" s="8">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="5">
+        <v>49875</v>
+      </c>
+      <c r="G33" s="8">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="5">
+        <v>10328</v>
+      </c>
+      <c r="G34" s="8">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="5">
+        <v>4987.5</v>
+      </c>
+      <c r="G35" s="8">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="5">
+        <v>87541</v>
+      </c>
+      <c r="G36" s="8">
+        <v>18620</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="5">
+        <v>41432</v>
+      </c>
+      <c r="G37" s="8">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="5">
+        <v>60000</v>
+      </c>
+      <c r="G38" s="8">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="5">
+        <v>1400000</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1200000</v>
+      </c>
+      <c r="G40" s="8">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="5">
+        <v>492100</v>
+      </c>
+      <c r="G41" s="8">
+        <v>230664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1550</v>
+      </c>
+      <c r="G42" s="8">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="5">
+        <v>16000</v>
+      </c>
+      <c r="G43" s="8">
+        <v>11525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
